--- a/data/trans_orig/Q5418_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de lavarse la ropa en 2023</t>
+          <t>Población según si es capaz de lavarse la ropa en 2023 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>14685</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>27997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>32778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38036</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55476</t>
+          <t>56127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13151</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>25236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20777</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32908</t>
+          <t>32957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36161</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53509</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100706</t>
+          <t>100573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>118159</t>
+          <t>117495</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>119831</t>
+          <t>118327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>134722</t>
+          <t>133969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>225556</t>
+          <t>222895</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247403</t>
+          <t>246546</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,34%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8854</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19912</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33290</t>
+          <t>33602</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32137</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49286</t>
+          <t>48404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20671</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31285</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>29788</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46575</t>
+          <t>46081</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125060</t>
+          <t>124009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139995</t>
+          <t>139103</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159599</t>
+          <t>159908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>177556</t>
+          <t>176728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288878</t>
+          <t>290601</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312813</t>
+          <t>312722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,54%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11655</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2898</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37118</t>
+          <t>37708</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>38102</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2193</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>10167</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31333</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>32674</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117801</t>
+          <t>116783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128736</t>
+          <t>128750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294995</t>
+          <t>296270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354479</t>
+          <t>353186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426421</t>
+          <t>427207</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482757</t>
+          <t>483595</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13147</t>
+          <t>13375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26917</t>
+          <t>27404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22779</t>
+          <t>22714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39576</t>
+          <t>39948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19366</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22540</t>
+          <t>22108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>37272</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>52556</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>170919</t>
+          <t>171362</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>186037</t>
+          <t>185974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>215458</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>235190</t>
+          <t>234931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>392773</t>
+          <t>392923</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417923</t>
+          <t>417548</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41302</t>
+          <t>41246</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62975</t>
+          <t>62413</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111061</t>
+          <t>110724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>89158</t>
+          <t>90294</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162603</t>
+          <t>163767</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39900</t>
+          <t>40145</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61915</t>
+          <t>61651</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50241</t>
+          <t>48469</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119590</t>
+          <t>119678</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94743</t>
+          <t>92739</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>168004</t>
+          <t>167801</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,99%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>531462</t>
+          <t>530481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>560694</t>
+          <t>558940</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>805647</t>
+          <t>805362</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>933379</t>
+          <t>937782</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1354839</t>
+          <t>1353126</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1495055</t>
+          <t>1496653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5418_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5418_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20155</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27997</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>27378</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>21583</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32778</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>46313</t>
+          <t>48282</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38878</t>
+          <t>39458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56127</t>
+          <t>58294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>18196</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25236</t>
+          <t>27475</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26414</t>
+          <t>28393</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20631</t>
+          <t>22119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>35497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>44610</t>
+          <t>48126</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>39552</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54290</t>
+          <t>58170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>109732</t>
+          <t>122677</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100573</t>
+          <t>113214</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117495</t>
+          <t>130580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126591</t>
+          <t>135258</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118327</t>
+          <t>125928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133969</t>
+          <t>143004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236322</t>
+          <t>257935</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>222895</t>
+          <t>244813</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>270270</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>76,27%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13807</t>
+          <t>14398</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9546</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>20029</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33602</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>39431</t>
+          <t>42588</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>34443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48404</t>
+          <t>52381</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,46%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>15009</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>9550</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20290</t>
+          <t>23404</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23941</t>
+          <t>26320</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>19323</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31571</t>
+          <t>33555</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>37448</t>
+          <t>41330</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29788</t>
+          <t>32584</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46081</t>
+          <t>52288</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>132800</t>
+          <t>148797</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124009</t>
+          <t>139712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>139103</t>
+          <t>155629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>169181</t>
+          <t>187529</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159908</t>
+          <t>177962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>176728</t>
+          <t>197091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>301982</t>
+          <t>336325</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290601</t>
+          <t>323524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>312722</t>
+          <t>348850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,01%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6214</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3720</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14220</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20434</t>
+          <t>22516</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>38102</t>
+          <t>31136</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5369</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10167</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11810</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2506</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5676</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32674</t>
+          <t>27057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>123876</t>
+          <t>145069</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116783</t>
+          <t>138113</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128750</t>
+          <t>150314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>334226</t>
+          <t>146228</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296270</t>
+          <t>138004</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353186</t>
+          <t>153563</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>458103</t>
+          <t>291297</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>427207</t>
+          <t>280195</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>483595</t>
+          <t>300175</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>495716</t>
+          <t>333066</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>495716</t>
+          <t>333066</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>495716</t>
+          <t>333066</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>11035</t>
+          <t>11339</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>17444</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19394</t>
+          <t>22007</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13375</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>33347</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22714</t>
+          <t>25414</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>43875</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7808</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18652</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>29291</t>
+          <t>32080</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22108</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>41251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>41901</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33122</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52556</t>
+          <t>55383</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>179595</t>
+          <t>189132</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171362</t>
+          <t>181390</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185974</t>
+          <t>195409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>226346</t>
+          <t>240633</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>216388</t>
+          <t>230220</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>234931</t>
+          <t>250868</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>405941</t>
+          <t>429765</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>392923</t>
+          <t>415435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417548</t>
+          <t>442325</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>203240</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>203240</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203240</t>
+          <t>213184</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>478271</t>
+          <t>507904</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>478271</t>
+          <t>507904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>478271</t>
+          <t>507904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>53288</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>43345</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62413</t>
+          <t>65919</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>85395</t>
+          <t>93446</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43514</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110724</t>
+          <t>107338</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>136607</t>
+          <t>146734</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>90294</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163767</t>
+          <t>166209</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49681</t>
+          <t>53897</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>40145</t>
+          <t>42135</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61651</t>
+          <t>66172</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91457</t>
+          <t>99604</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48469</t>
+          <t>85092</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119678</t>
+          <t>114949</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>141138</t>
+          <t>153501</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>92739</t>
+          <t>134890</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167801</t>
+          <t>171005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>546003</t>
+          <t>605674</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>530481</t>
+          <t>589183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>558940</t>
+          <t>620165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>856345</t>
+          <t>709648</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>805362</t>
+          <t>691578</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>937782</t>
+          <t>728881</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1402348</t>
+          <t>1315322</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1353126</t>
+          <t>1290698</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1496653</t>
+          <t>1338615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>82,86%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>646896</t>
+          <t>712859</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1680093</t>
+          <t>1615557</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
